--- a/artfynd/A 43726-2025 artfynd.xlsx
+++ b/artfynd/A 43726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533053</v>
       </c>
       <c r="B2" t="n">
-        <v>92026</v>
+        <v>92032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128533054</v>
       </c>
       <c r="B3" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128533055</v>
       </c>
       <c r="B4" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43726-2025 artfynd.xlsx
+++ b/artfynd/A 43726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533053</v>
       </c>
       <c r="B2" t="n">
-        <v>92032</v>
+        <v>92038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43726-2025 artfynd.xlsx
+++ b/artfynd/A 43726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533053</v>
       </c>
       <c r="B2" t="n">
-        <v>92038</v>
+        <v>92040</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128533054</v>
       </c>
       <c r="B3" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128533055</v>
       </c>
       <c r="B4" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43726-2025 artfynd.xlsx
+++ b/artfynd/A 43726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533053</v>
       </c>
       <c r="B2" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43726-2025 artfynd.xlsx
+++ b/artfynd/A 43726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533053</v>
       </c>
       <c r="B2" t="n">
-        <v>92041</v>
+        <v>92068</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128533054</v>
       </c>
       <c r="B3" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128533055</v>
       </c>
       <c r="B4" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43726-2025 artfynd.xlsx
+++ b/artfynd/A 43726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533053</v>
       </c>
       <c r="B2" t="n">
-        <v>92068</v>
+        <v>92073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128533054</v>
       </c>
       <c r="B3" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128533055</v>
       </c>
       <c r="B4" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43726-2025 artfynd.xlsx
+++ b/artfynd/A 43726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533053</v>
       </c>
       <c r="B2" t="n">
-        <v>92073</v>
+        <v>92078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43726-2025 artfynd.xlsx
+++ b/artfynd/A 43726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533053</v>
       </c>
       <c r="B2" t="n">
-        <v>92078</v>
+        <v>92082</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128533054</v>
       </c>
       <c r="B3" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128533055</v>
       </c>
       <c r="B4" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43726-2025 artfynd.xlsx
+++ b/artfynd/A 43726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533053</v>
       </c>
       <c r="B2" t="n">
-        <v>92082</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128533054</v>
       </c>
       <c r="B3" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128533055</v>
       </c>
       <c r="B4" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43726-2025 artfynd.xlsx
+++ b/artfynd/A 43726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533053</v>
       </c>
       <c r="B2" t="n">
-        <v>92090</v>
+        <v>92095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128533054</v>
       </c>
       <c r="B3" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128533055</v>
       </c>
       <c r="B4" t="n">
-        <v>78786</v>
+        <v>78791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43726-2025 artfynd.xlsx
+++ b/artfynd/A 43726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533053</v>
       </c>
       <c r="B2" t="n">
-        <v>92095</v>
+        <v>92103</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128533054</v>
       </c>
       <c r="B3" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128533055</v>
       </c>
       <c r="B4" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43726-2025 artfynd.xlsx
+++ b/artfynd/A 43726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533053</v>
       </c>
       <c r="B2" t="n">
-        <v>92103</v>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128533054</v>
+        <v>128533055</v>
       </c>
       <c r="B3" t="n">
-        <v>80140</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672601</v>
+        <v>672649</v>
       </c>
       <c r="R3" t="n">
-        <v>7162508</v>
+        <v>7162532</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128533055</v>
+        <v>128533054</v>
       </c>
       <c r="B4" t="n">
-        <v>78792</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672649</v>
+        <v>672601</v>
       </c>
       <c r="R4" t="n">
-        <v>7162532</v>
+        <v>7162508</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 43726-2025 artfynd.xlsx
+++ b/artfynd/A 43726-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533053</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533055</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,8 +1005,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533054</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>